--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.81696</v>
+        <v>16.78925</v>
       </c>
       <c r="D2" t="n">
-        <v>16.84444</v>
+        <v>16.44886</v>
       </c>
       <c r="E2" t="n">
-        <v>16.56852</v>
+        <v>16.77699</v>
       </c>
       <c r="F2" t="n">
-        <v>41.25118</v>
+        <v>42.25081</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05001</v>
+        <v>0.05071</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83702</v>
+        <v>1.80205</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.71461</v>
+        <v>16.84939</v>
       </c>
       <c r="D3" t="n">
-        <v>16.7907</v>
+        <v>16.5234</v>
       </c>
       <c r="E3" t="n">
-        <v>16.46589</v>
+        <v>16.54263</v>
       </c>
       <c r="F3" t="n">
-        <v>42.71556</v>
+        <v>42.64007</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05088</v>
+        <v>0.05023</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84229</v>
+        <v>1.81897</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.5639</v>
+        <v>16.79487</v>
       </c>
       <c r="D4" t="n">
-        <v>16.24498</v>
+        <v>16.48089</v>
       </c>
       <c r="E4" t="n">
-        <v>16.66119</v>
+        <v>16.59065</v>
       </c>
       <c r="F4" t="n">
-        <v>42.2523</v>
+        <v>42.96364</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05041</v>
+        <v>0.05149</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81579</v>
+        <v>1.81505</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.76414</v>
+        <v>16.56393</v>
       </c>
       <c r="D6" t="n">
-        <v>16.21069</v>
+        <v>16.02894</v>
       </c>
       <c r="E6" t="n">
-        <v>16.55313</v>
+        <v>16.46081</v>
       </c>
       <c r="F6" t="n">
-        <v>21.59619</v>
+        <v>21.431</v>
       </c>
       <c r="G6" t="n">
-        <v>33.8248</v>
+        <v>34.46447</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.49544</v>
+        <v>16.63451</v>
       </c>
       <c r="D7" t="n">
-        <v>16.13711</v>
+        <v>15.73538</v>
       </c>
       <c r="E7" t="n">
-        <v>16.34405</v>
+        <v>16.26185</v>
       </c>
       <c r="F7" t="n">
-        <v>21.56171</v>
+        <v>21.80329</v>
       </c>
       <c r="G7" t="n">
-        <v>33.77364</v>
+        <v>33.84634</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.68652</v>
+        <v>16.77973</v>
       </c>
       <c r="D8" t="n">
-        <v>15.97202</v>
+        <v>15.89191</v>
       </c>
       <c r="E8" t="n">
-        <v>16.25855</v>
+        <v>16.54129</v>
       </c>
       <c r="F8" t="n">
-        <v>21.68954</v>
+        <v>21.93756</v>
       </c>
       <c r="G8" t="n">
-        <v>34.49432</v>
+        <v>33.85762</v>
       </c>
     </row>
   </sheetData>
